--- a/MyProject/OfficeCLI/REKENING KORAN/MANDIRI/Rekap_Rekening_Koran_Mandiri_2026.xlsx
+++ b/MyProject/OfficeCLI/REKENING KORAN/MANDIRI/Rekap_Rekening_Koran_Mandiri_2026.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="525" windowWidth="19815" windowHeight="7365" activeTab="3"/>
+    <workbookView xWindow="390" yWindow="525" windowWidth="19815" windowHeight="7365" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ringkasan Eksekutif" sheetId="1" r:id="rId1"/>
@@ -10446,6 +10446,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
